--- a/.planning/TRAEVY-DEVICE-CHECKS.xlsx
+++ b/.planning/TRAEVY-DEVICE-CHECKS.xlsx
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,26 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -96,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +148,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -495,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -771,6 +803,90 @@
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>If the backend misbehaves on nodejs24, the previous Cloud Run revision is api-00003-tih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>UAT SESSION 2026-07-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Reported by</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>User ran P1 + the v0.1 backlog on device</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48 scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Still open</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N05 (GPS drift), N08 + N15 (widget — run as one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N09-N11, N13, V42-V45 — all need the live backend / signed-in account. User revisiting last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>V15 — no pre-Phase-3 rows exist on a fresh install</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NOT UAT, still open</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>G01 Data Safety declaration, G02 debug signing — both block a Play release</t>
         </is>
       </c>
     </row>
@@ -1248,9 +1364,21 @@
           <t>commit a5fffce</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -1288,9 +1416,21 @@
           <t>commit a5fffce</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -1328,9 +1468,21 @@
           <t>commit a5fffce</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -1368,9 +1520,21 @@
           <t>commit ef4d03e; BACKLOG 999.2</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -1408,8 +1572,12 @@
           <t>Phase 27 / commit 675fec1</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>OPEN — needs a 15-min stationary run OUTDOORS/at a window. Indoors the 30m accuracy gate rejects samples, so 0m would be a false pass. Read the LIVE tile: a stationary trip is &lt;100m so it is discarded on Stop and never reaches history.</t>
+        </is>
+      </c>
       <c r="J15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
@@ -1448,9 +1616,21 @@
           <t>Phase 27 / commit 26b017b</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1488,9 +1668,21 @@
           <t>Phase 27 / commit 5f75640</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -1528,8 +1720,12 @@
           <t>Phase 28 / commit 88092b7</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>OPEN — run together with N15 as one widget session.</t>
+        </is>
+      </c>
       <c r="J18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
@@ -1568,9 +1764,21 @@
           <t>Phase 29 / commit bf96bbb</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync — needs live backend + signed-in account.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -1608,9 +1816,21 @@
           <t>Phase 29 / commit bf96bbb</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync — needs live backend + signed-in account.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -1648,9 +1868,21 @@
           <t>Phase 29 / commit bf96bbb</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync — needs live backend + two-device setup.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -1688,9 +1920,21 @@
           <t>25.1-HUMAN-UAT.md</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -1728,9 +1972,21 @@
           <t>commit e76f52c; revision api-00004-bug</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync — full authenticated round trip.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -1768,9 +2024,21 @@
           <t>phases/21-home-office-locations-geofence/21-UAT.md</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -1808,8 +2076,12 @@
           <t>phases/22-home-screen-widget/22-UAT.md</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>OPEN — 3 scenarios: (1) add widget, (2) toggle tracking from widget, (3) widget visually updates state. Overlaps N08; one pass closes both.</t>
+        </is>
+      </c>
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="58" customHeight="1">
@@ -1848,9 +2120,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="12" t="inlineStr"/>
-      <c r="J26" s="12" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -1888,9 +2172,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="12" t="inlineStr"/>
-      <c r="J27" s="12" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -1928,9 +2224,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="12" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -1968,9 +2276,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="12" t="inlineStr"/>
-      <c r="J29" s="12" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -2008,9 +2328,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="12" t="inlineStr"/>
-      <c r="J30" s="12" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -2048,9 +2380,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="12" t="inlineStr"/>
-      <c r="J31" s="12" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -2088,9 +2432,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="12" t="inlineStr"/>
-      <c r="J32" s="12" t="inlineStr"/>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -2128,9 +2484,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="12" t="inlineStr"/>
-      <c r="J33" s="12" t="inlineStr"/>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -2168,9 +2536,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="12" t="inlineStr"/>
-      <c r="J34" s="12" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -2208,9 +2588,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="12" t="inlineStr"/>
-      <c r="J35" s="12" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -2248,9 +2640,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="12" t="inlineStr"/>
-      <c r="J36" s="12" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -2288,9 +2692,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="12" t="inlineStr"/>
-      <c r="J37" s="12" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -2328,9 +2744,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="12" t="inlineStr"/>
-      <c r="J38" s="12" t="inlineStr"/>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -2368,9 +2796,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="12" t="inlineStr"/>
-      <c r="J39" s="12" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -2408,9 +2848,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="12" t="inlineStr"/>
-      <c r="J40" s="12" t="inlineStr"/>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>N-A on a fresh install. directionBackfillProvider (app.dart:50) only re-labels rows with direction='unknown', which only a pre-Phase-3 build could create. Nothing to observe unless upgrading over an old build. Not a gap.</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -2448,9 +2900,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="12" t="inlineStr"/>
-      <c r="J41" s="12" t="inlineStr"/>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -2488,9 +2952,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="12" t="inlineStr"/>
-      <c r="J42" s="12" t="inlineStr"/>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -2528,9 +3004,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="12" t="inlineStr"/>
-      <c r="J43" s="12" t="inlineStr"/>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -2568,9 +3056,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="12" t="inlineStr"/>
-      <c r="J44" s="12" t="inlineStr"/>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -2608,9 +3108,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="12" t="inlineStr"/>
-      <c r="J45" s="12" t="inlineStr"/>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -2648,9 +3160,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="12" t="inlineStr"/>
-      <c r="J46" s="12" t="inlineStr"/>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -2688,9 +3212,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="12" t="inlineStr"/>
-      <c r="J47" s="12" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -2728,9 +3264,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="12" t="inlineStr"/>
-      <c r="J48" s="12" t="inlineStr"/>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
@@ -2768,9 +3316,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="12" t="inlineStr"/>
-      <c r="J49" s="12" t="inlineStr"/>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
@@ -2808,9 +3368,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="12" t="inlineStr"/>
-      <c r="J50" s="12" t="inlineStr"/>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -2848,9 +3420,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="12" t="inlineStr"/>
-      <c r="J51" s="12" t="inlineStr"/>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -2888,9 +3472,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="12" t="inlineStr"/>
-      <c r="J52" s="12" t="inlineStr"/>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -2928,9 +3524,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="12" t="inlineStr"/>
-      <c r="J53" s="12" t="inlineStr"/>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -2968,9 +3576,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="12" t="inlineStr"/>
-      <c r="J54" s="12" t="inlineStr"/>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -3008,9 +3628,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="12" t="inlineStr"/>
-      <c r="J55" s="12" t="inlineStr"/>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -3048,9 +3680,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="12" t="inlineStr"/>
-      <c r="J56" s="12" t="inlineStr"/>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -3088,9 +3732,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="12" t="inlineStr"/>
-      <c r="J57" s="12" t="inlineStr"/>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -3128,9 +3784,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="12" t="inlineStr"/>
-      <c r="J58" s="12" t="inlineStr"/>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -3168,9 +3836,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="12" t="inlineStr"/>
-      <c r="J59" s="12" t="inlineStr"/>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -3208,9 +3888,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="12" t="inlineStr"/>
-      <c r="J60" s="12" t="inlineStr"/>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
@@ -3248,9 +3940,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr"/>
-      <c r="I61" s="12" t="inlineStr"/>
-      <c r="J61" s="12" t="inlineStr"/>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
@@ -3288,9 +3992,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr"/>
-      <c r="I62" s="12" t="inlineStr"/>
-      <c r="J62" s="12" t="inlineStr"/>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
@@ -3328,9 +4044,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr"/>
-      <c r="I63" s="12" t="inlineStr"/>
-      <c r="J63" s="12" t="inlineStr"/>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -3368,9 +4096,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr"/>
-      <c r="I64" s="12" t="inlineStr"/>
-      <c r="J64" s="12" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
@@ -3408,9 +4148,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr"/>
-      <c r="I65" s="12" t="inlineStr"/>
-      <c r="J65" s="12" t="inlineStr"/>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
@@ -3448,9 +4200,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr"/>
-      <c r="I66" s="12" t="inlineStr"/>
-      <c r="J66" s="12" t="inlineStr"/>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>Passed in the 2026-07-21 UAT session.</t>
+        </is>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -3488,9 +4252,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr"/>
-      <c r="I67" s="12" t="inlineStr"/>
-      <c r="J67" s="12" t="inlineStr"/>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync.</t>
+        </is>
+      </c>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -3528,9 +4304,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="12" t="inlineStr"/>
-      <c r="J68" s="12" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync.</t>
+        </is>
+      </c>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -3568,9 +4356,21 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr"/>
-      <c r="I69" s="12" t="inlineStr"/>
-      <c r="J69" s="12" t="inlineStr"/>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync.</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -3608,15 +4408,27 @@
           <t>v0.1-DEVICE-CHECKLIST.md</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr"/>
-      <c r="I70" s="12" t="inlineStr"/>
-      <c r="J70" s="12" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>Deferred with backend/sync.</t>
+        </is>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J70"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,Blocked,N-A,Skipped"</formula1>
+      <formula1>"Pass,Fail,Blocked,Deferred,N-A,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/.planning/TRAEVY-DEVICE-CHECKS.xlsx
+++ b/.planning/TRAEVY-DEVICE-CHECKS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Checks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$J$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$J$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +165,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -808,7 +819,6 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -816,7 +826,6 @@
           <t>UAT SESSION 2026-07-21</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -887,6 +896,66 @@
       <c r="B35" t="inlineStr">
         <is>
           <t>G01 Data Safety declaration, G02 debug signing — both block a Play release</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>UAT BATCHED INTO PHASE 36 — 2026-07-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Phase 36 rewrites the widget layout/icons AND the notification Stop action. Verifying either beforehand would only need redoing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>New checks</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P36-A1..A6 (notification ranking), P36-B1..B5 (auto-pause prompt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Moved in</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N05 -&gt; C1, N08 + N15 -&gt; C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Watch item</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P36-A5 is the only unproven claim from the 2026-07-21 notification work. If the notification does not return within ~5s after a swipe, that is a real bug.</t>
         </is>
       </c>
     </row>
@@ -901,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1537,48 +1606,48 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>N05</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>P1 Unverified</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Phase 27 — TRACK-14</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Standing still does not accumulate distance</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Start a trip, put the phone down, wait ~15 minutes without moving. Distance must stay ~0. Previously ~220 m accumulated over 14 min from GPS jitter.</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Requires real GPS noise over real time; the emulator's synthetic fixes do not reproduce drift.</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>Phase 27 / commit 675fec1</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>OPEN — needs a 15-min stationary run OUTDOORS/at a window. Indoors the 30m accuracy gate rejects samples, so 0m would be a false pass. Read the LIVE tile: a stationary trip is &lt;100m so it is discarded on Stop and never reaches history.</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr"/>
+      <c r="H15" s="18" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>MOVED to Phase 36 UAT batch as C1 (2026-07-22). Independent of Phase 36 — can be run any time. Run OUTDOORS/at a window; indoors the 30m accuracy gate makes 0m a FALSE pass. Read the LIVE tile.</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -1685,48 +1754,48 @@
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>N08</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>P1 Unverified</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Phase 28 — WIDGET-02/03</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>Home-screen widget adapts to size and shows correct stats</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Add the widget. Resize wide (4x2): rich stats appear. Shrink to 2x2: compact layout returns. Idle numbers must match the in-app Stats screen. Start a trip: speed and moving/stuck update ~every 5s; pause shows the PAUSED chip. Start/Pause/Stop buttons still work from the widget.</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>RemoteViews(Map&lt;SizeF,...&gt;) selection happens in the launcher process, outside the app entirely.</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Phase 28 / commit 88092b7</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>OPEN — run together with N15 as one widget session.</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>MOVED to Phase 36 UAT batch as C2 (2026-07-22). Deferred deliberately: 36-01 replaces the widget stop icon and resizing, so testing now would be thrown away.</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -2041,48 +2110,48 @@
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>N15</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>P1 Unverified</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Phase 22 — home-screen widget</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Complete the stalled 22-UAT session (all 3 widget scenarios)</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Session stalled at test 1 of 3, 'awaiting user response' since 2026-06-09. Overlaps the Phase 28 widget item above — run together.</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>Launcher-process behaviour.</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>phases/22-home-screen-widget/22-UAT.md</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>OPEN — 3 scenarios: (1) add widget, (2) toggle tracking from widget, (3) widget visually updates state. Overlaps N08; one pass closes both.</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr"/>
+      <c r="H25" s="18" t="inlineStr"/>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>MOVED to Phase 36 UAT batch as C2 (2026-07-22) — merged with N08 into one widget session.</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr"/>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -4424,10 +4493,494 @@
         </is>
       </c>
     </row>
+    <row r="71" ht="58" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>P36-A1</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Recording notification sits at the TOP of the shade, not the Silent section</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>Start a trip, pull down the shade.</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Shade ranking is an OS behaviour; no widget test can observe it.</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="n"/>
+    </row>
+    <row r="72" ht="58" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>P36-A2</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>Heads-up ONCE at trip start, then silent for the rest of the trip</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>Watch at trip start, then for the next few minutes. onlyAlertOnce must suppress re-alerting at the ~5s refresh.</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Requires observing real notification alerting over time.</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="n"/>
+    </row>
+    <row r="73" ht="58" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>P36-A3</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>Survives the lock screen</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>Start a trip, lock the phone, try to swipe it away from the lockscreen.</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Android guarantees this, but it has never been confirmed for this app.</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J73" s="18" t="n"/>
+    </row>
+    <row r="74" ht="58" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>P36-A4</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>Survives "Clear all"</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>Start a trip, pull down the shade, hit Clear all.</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>OS-level behaviour.</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="n"/>
+    </row>
+    <row r="75" ht="58" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>P36-A5</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Deliberate swipe while UNLOCKED -&gt; returns within ~5s</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Start a trip, unlock, swipe the recording notification away, count the seconds.</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>THE ONE UNPROVEN CLAIM from 2026-07-21. Follows from _maybeRefreshNotification re-posting on a 5s throttle, but has never been observed. If it does NOT return, that is a real bug.</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="n"/>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J75" s="18" t="n"/>
+    </row>
+    <row r="76" ht="58" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>P36-A6</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Notification ranking</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>After upgrade, exactly ONE "Active commute" channel in system settings</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Install an older build, upgrade to this one, open Settings &gt; Apps &gt; Traevy &gt; Notifications.</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>The legacy channel delete only matters on an UPGRADE path; a fresh install can never surface this.</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>f5dfe7a</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J76" s="18" t="n"/>
+    </row>
+    <row r="77" ht="58" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>P36-B1</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>Auto-pause prompt</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Prompt appears as a heads-up ABOVE the recording notification</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>15 min stationary mid-trip with auto-pause ON.</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Heads-up presentation is not observable in tests.</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>318b005</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="n"/>
+    </row>
+    <row r="78" ht="58" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>P36-B2</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>Auto-pause prompt</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Tapping Pause opens the app + shows the dialog, does NOT pause silently</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Tap Pause on the prompt notification.</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>The whole point of the change; only an end-to-end tap proves the relay works.</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>318b005</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="n"/>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J78" s="18" t="n"/>
+    </row>
+    <row r="79" ht="58" customHeight="1">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>P36-B3</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>Auto-pause prompt</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Confirming in the dialog pauses the trip</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>Tap Pause in the dialog.</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>End-to-end through two isolates.</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>318b005</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J79" s="18" t="n"/>
+    </row>
+    <row r="80" ht="58" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>P36-B4</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Auto-pause prompt</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>NEGATIVE CASE: swiping the prompt away leaves the trip recording</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>Swipe the prompt instead of tapping it.</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>Phase 18 D-12 guarantee. Easy to skip when short on time; do not.</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>318b005</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J80" s="18" t="n"/>
+    </row>
+    <row r="81" ht="58" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>P36-B5</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>P1 Unverified</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>Auto-pause prompt</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Prompt and 36-03 Stop confirmation use the same dialog shape/wording</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>Compare both dialogs side by side after 36-03 lands.</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Phase 36 SC9; needs 36-03 built first.</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Phase 36 SC9</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>Owned by Phase 36 — run at phase close (2026-07-22).</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J70"/>
+  <autoFilter ref="A1:J81"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,Deferred,N-A,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
